--- a/BKQBF_TAB-3.xlsx
+++ b/BKQBF_TAB-3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0ddff5975960f05/Dcts_BK_compartilhado/BI_Arquivos_compartilhado/c_Sistema_BKQBF/BK_Compra_Perfeita/CPerfect_Files_GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{C30B5866-1CA3-4F73-BC97-BD861B109F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3486D7F1-7BB3-4F52-960B-F593182F12DA}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{C30B5866-1CA3-4F73-BC97-BD861B109F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E3AE9D4-A821-4610-B602-09610B22DCED}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="relatorio" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">relatorio!$A$1:$K$1342</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">relatorio!$A$1:$K$1504</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9029" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9028" uniqueCount="283">
   <si>
     <t>Setor</t>
   </si>
@@ -948,6 +948,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1273,7 +1277,7 @@
   <dimension ref="A1:K1504"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="21.5" customWidth="1"/>
+    <col min="5" max="5" width="27.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -32646,8 +32650,8 @@
       <c r="C897" t="s">
         <v>12</v>
       </c>
-      <c r="D897" t="s">
-        <v>117</v>
+      <c r="D897">
+        <v>7500029</v>
       </c>
       <c r="E897" t="s">
         <v>118</v>
@@ -53917,10 +53921,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1342" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K1342">
-    <sortCondition descending="1" ref="F2:F1342"/>
-    <sortCondition ref="D2:D1342"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K1504">
+    <sortCondition descending="1" ref="F2:F1504"/>
+    <sortCondition ref="D2:D1504"/>
   </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
